--- a/docs/tasks/인허가/20260909_2140_sound1-adc-table/스크립트/측정원본_수정후_20260910.xlsx
+++ b/docs/tasks/인허가/20260909_2140_sound1-adc-table/스크립트/측정원본_수정후_20260910.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EUNSU\.claude\jobs\00571323\tmp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A113DB-CA26-4359-9EF1-09EB320BECB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72779E01-801E-4D51-B33F-4B891177C90D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1.5세대 입력 음압 대비 ADC 출력 테이블" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="30">
   <si>
     <t>dBSPL</t>
   </si>
@@ -127,128 +127,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Microsoft GothicNeo"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>음압</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>dB SPL</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>ADC
-(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>멤브레인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>미적용</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>ADC
-(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>멤브레인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>고려</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>500C-2</t>
     </r>
     <r>
@@ -271,6 +149,48 @@
   </si>
   <si>
     <t>기구 조립</t>
+  </si>
+  <si>
+    <t>Sound1 입력 음압 대비 ADC 출력 테이블</t>
+  </si>
+  <si>
+    <t>음압
+dB SPL</t>
+  </si>
+  <si>
+    <t>1.5세대 ADC
+(멤브레인 미적용)</t>
+  </si>
+  <si>
+    <t>1.5세대 ADC
+(멤브레인 고려)</t>
+  </si>
+  <si>
+    <t>Sound1 ADC
+(PCB 상태)</t>
+  </si>
+  <si>
+    <t>Sound1 ADC
+(기구 조립 상태)</t>
+  </si>
+  <si>
+    <t>1.5세대와 Sound1 은 같은 스펙의 마이크를 쓴다. 그래서 1.5세대 테이블의 생성 규칙을 그대로 두고 Sound1 의 감쇠만 반영했다.
+ADC = floor(262143 x 10^((dB SPL - 120 + 감쇠) / 20)),  262143 = 2^18 - 1  (1.5세대 표가 내림으로 만들어져 있다)
+감쇠는 고음압 평탄 구간(80~110 dB SPL) 실측에서 구했다.  PCB 상태 -3.644 dB = 5 시료 평균 (참조용, 시험 대상이 아니다)
+기구 조립 -8.293 dB = 실측 6 시료의 상·하한 중앙 (판정용).  시험 허용 오차 +-5 dB 는 이 표에서 정확히 한 칸 위/아래다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>허용 범위 (PCB 상태)</t>
+  </si>
+  <si>
+    <t>+5 dB</t>
+  </si>
+  <si>
+    <t>-5 dB</t>
+  </si>
+  <si>
+    <t>허용 범위 (기구 조립)</t>
   </si>
 </sst>
 </file>
@@ -349,30 +269,31 @@
       <charset val="129"/>
     </font>
     <font>
+      <b/>
+      <u/>
       <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft GothicNeo"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF00B050"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
+      <b/>
+      <sz val="10"/>
       <name val="맑은 고딕"/>
-      <family val="2"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
   </fonts>
@@ -403,12 +324,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8E8E8"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -457,11 +377,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -488,20 +423,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -513,6 +449,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1417,6 +1359,262 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-5828-442F-A87A-630108609633}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:v>허용 상한 (+5 dB)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="15875" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="808080"/>
+              </a:solidFill>
+              <a:prstDash val="dot"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Sound1 시료 측정 데이터'!$B$4:$B$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>110</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Sound1 시료 측정 데이터'!$AF$5:$AF$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>306</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>544</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>969</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1723</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3064</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5449</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9690</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>17232</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>30643</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>54492</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>96903</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-14C4-4362-849B-66D1E6E5B419}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:v>허용 하한 (-5 dB)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="15875" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="808080"/>
+              </a:solidFill>
+              <a:prstDash val="dot"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Sound1 시료 측정 데이터'!$B$4:$B$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>110</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Sound1 시료 측정 데이터'!$AG$5:$AG$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>306</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>544</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>969</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1723</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3064</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5449</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9690</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>17232</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>30643</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-14C4-4362-849B-66D1E6E5B419}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1959,17 +2157,17 @@
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="7"/>
-          <c:order val="7"/>
+          <c:idx val="8"/>
+          <c:order val="8"/>
           <c:tx>
-            <c:v>Sound1 산출 기준 (기구 조립)</c:v>
+            <c:v>허용 상한 (+5 dB)</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="808080"/>
               </a:solidFill>
-              <a:prstDash val="dash"/>
+              <a:prstDash val="dot"/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -2030,51 +2228,51 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sound1 시료 측정 데이터'!$AE$5:$AE$18</c:f>
+              <c:f>'Sound1 시료 측정 데이터'!$AH$5:$AH$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>17</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>31</c:v>
+                  <c:v>56</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>56</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100</c:v>
+                  <c:v>179</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>179</c:v>
+                  <c:v>319</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>319</c:v>
+                  <c:v>567</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>567</c:v>
+                  <c:v>1008</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1008</c:v>
+                  <c:v>1794</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1794</c:v>
+                  <c:v>3190</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3190</c:v>
+                  <c:v>5673</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5673</c:v>
+                  <c:v>10089</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>10089</c:v>
+                  <c:v>17942</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>17942</c:v>
+                  <c:v>31907</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>31907</c:v>
+                  <c:v>56739</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2082,7 +2280,135 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-09F3-46E0-920B-6E4F9EFEAB26}"/>
+              <c16:uniqueId val="{00000000-3551-42B7-B6E6-6AA1E1C524E0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:v>허용 하한 (-5 dB)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="15875" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="808080"/>
+              </a:solidFill>
+              <a:prstDash val="dot"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Sound1 시료 측정 데이터'!$B$4:$B$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>110</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Sound1 시료 측정 데이터'!$AI$5:$AI$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>179</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>319</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>567</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1008</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1794</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3190</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5673</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>10089</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>17942</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3551-42B7-B6E6-6AA1E1C524E0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2218,6 +2544,134 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000006-7B9F-4EF5-B148-2803F1FD8D15}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:v>Sound1 산출 기준 (기구 조립)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Sound1 시료 측정 데이터'!$B$4:$B$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>110</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Sound1 시료 측정 데이터'!$AE$5:$AE$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>179</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>319</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>567</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1008</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1794</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3190</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5673</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10089</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>17942</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>31907</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-09F3-46E0-920B-6E4F9EFEAB26}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4570,1038 +5024,1642 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11E10556-28C7-4DB4-93AC-87A1ED846803}">
-  <dimension ref="B2:D94"/>
+  <dimension ref="B2:F100"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="9"/>
-    <col min="2" max="4" width="14.625" style="9" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="9"/>
+    <col min="2" max="6" width="17.375" style="9" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="12" t="s">
+    <row r="2" spans="2:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+    </row>
+    <row r="3" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="2:6" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+    </row>
+    <row r="5" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+    </row>
+    <row r="6" spans="2:6" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+    </row>
+    <row r="7" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="2:6" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="12">
+        <v>29</v>
+      </c>
+      <c r="C9" s="12">
+        <v>7</v>
+      </c>
+      <c r="D9" s="12">
+        <v>7</v>
+      </c>
+      <c r="E9" s="12">
+        <v>4</v>
+      </c>
+      <c r="F9" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="12">
+        <v>30</v>
+      </c>
+      <c r="C10" s="12">
+        <v>8</v>
+      </c>
+      <c r="D10" s="12">
+        <v>7</v>
+      </c>
+      <c r="E10" s="12">
+        <v>5</v>
+      </c>
+      <c r="F10" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="12">
+        <v>31</v>
+      </c>
+      <c r="C11" s="12">
+        <v>9</v>
+      </c>
+      <c r="D11" s="12">
+        <v>7</v>
+      </c>
+      <c r="E11" s="12">
+        <v>6</v>
+      </c>
+      <c r="F11" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="12">
+        <v>32</v>
+      </c>
+      <c r="C12" s="12">
+        <v>10</v>
+      </c>
+      <c r="D12" s="12">
+        <v>7</v>
+      </c>
+      <c r="E12" s="12">
+        <v>6</v>
+      </c>
+      <c r="F12" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="12">
+        <v>33</v>
+      </c>
+      <c r="C13" s="12">
+        <v>11</v>
+      </c>
+      <c r="D13" s="12">
+        <v>8</v>
+      </c>
+      <c r="E13" s="12">
+        <v>7</v>
+      </c>
+      <c r="F13" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="12">
+        <v>34</v>
+      </c>
+      <c r="C14" s="12">
+        <v>13</v>
+      </c>
+      <c r="D14" s="12">
+        <v>9</v>
+      </c>
+      <c r="E14" s="12">
+        <v>8</v>
+      </c>
+      <c r="F14" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="12">
+        <v>35</v>
+      </c>
+      <c r="C15" s="12">
+        <v>14</v>
+      </c>
+      <c r="D15" s="12">
+        <v>10</v>
+      </c>
+      <c r="E15" s="12">
+        <v>9</v>
+      </c>
+      <c r="F15" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="12">
+        <v>36</v>
+      </c>
+      <c r="C16" s="12">
+        <v>16</v>
+      </c>
+      <c r="D16" s="12">
+        <v>11</v>
+      </c>
+      <c r="E16" s="12">
+        <v>10</v>
+      </c>
+      <c r="F16" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="12">
+        <v>37</v>
+      </c>
+      <c r="C17" s="12">
+        <v>18</v>
+      </c>
+      <c r="D17" s="12">
+        <v>13</v>
+      </c>
+      <c r="E17" s="12">
+        <v>12</v>
+      </c>
+      <c r="F17" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="12">
+        <v>38</v>
+      </c>
+      <c r="C18" s="12">
+        <v>20</v>
+      </c>
+      <c r="D18" s="12">
+        <v>14</v>
+      </c>
+      <c r="E18" s="12">
+        <v>13</v>
+      </c>
+      <c r="F18" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="12">
+        <v>39</v>
+      </c>
+      <c r="C19" s="12">
+        <v>23</v>
+      </c>
+      <c r="D19" s="12">
+        <v>16</v>
+      </c>
+      <c r="E19" s="12">
         <v>15</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="10" t="s">
+      <c r="F19" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="12">
+        <v>40</v>
+      </c>
+      <c r="C20" s="12">
+        <v>26</v>
+      </c>
+      <c r="D20" s="12">
+        <v>18</v>
+      </c>
+      <c r="E20" s="12">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="3">
+      <c r="F20" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="12">
+        <v>41</v>
+      </c>
+      <c r="C21" s="12">
         <v>29</v>
       </c>
-      <c r="C3" s="3">
-        <v>7</v>
-      </c>
-      <c r="D3" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="3">
+      <c r="D21" s="12">
+        <v>20</v>
+      </c>
+      <c r="E21" s="12">
+        <v>19</v>
+      </c>
+      <c r="F21" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="12">
+        <v>42</v>
+      </c>
+      <c r="C22" s="12">
+        <v>33</v>
+      </c>
+      <c r="D22" s="12">
+        <v>23</v>
+      </c>
+      <c r="E22" s="12">
+        <v>21</v>
+      </c>
+      <c r="F22" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="12">
+        <v>43</v>
+      </c>
+      <c r="C23" s="12">
+        <v>37</v>
+      </c>
+      <c r="D23" s="12">
+        <v>26</v>
+      </c>
+      <c r="E23" s="12">
+        <v>24</v>
+      </c>
+      <c r="F23" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="12">
+        <v>44</v>
+      </c>
+      <c r="C24" s="12">
+        <v>41</v>
+      </c>
+      <c r="D24" s="12">
+        <v>29</v>
+      </c>
+      <c r="E24" s="12">
+        <v>27</v>
+      </c>
+      <c r="F24" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="12">
+        <v>45</v>
+      </c>
+      <c r="C25" s="12">
+        <v>46</v>
+      </c>
+      <c r="D25" s="12">
+        <v>33</v>
+      </c>
+      <c r="E25" s="12">
         <v>30</v>
       </c>
-      <c r="C4" s="3">
-        <v>8</v>
-      </c>
-      <c r="D4" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="3">
+      <c r="F25" s="12">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="12">
+        <v>46</v>
+      </c>
+      <c r="C26" s="12">
+        <v>52</v>
+      </c>
+      <c r="D26" s="12">
+        <v>37</v>
+      </c>
+      <c r="E26" s="12">
+        <v>34</v>
+      </c>
+      <c r="F26" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="12">
+        <v>47</v>
+      </c>
+      <c r="C27" s="12">
+        <v>58</v>
+      </c>
+      <c r="D27" s="12">
+        <v>41</v>
+      </c>
+      <c r="E27" s="12">
+        <v>38</v>
+      </c>
+      <c r="F27" s="12">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="12">
+        <v>48</v>
+      </c>
+      <c r="C28" s="12">
+        <v>65</v>
+      </c>
+      <c r="D28" s="12">
+        <v>46</v>
+      </c>
+      <c r="E28" s="12">
+        <v>43</v>
+      </c>
+      <c r="F28" s="12">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="12">
+        <v>49</v>
+      </c>
+      <c r="C29" s="12">
+        <v>73</v>
+      </c>
+      <c r="D29" s="12">
+        <v>52</v>
+      </c>
+      <c r="E29" s="12">
+        <v>48</v>
+      </c>
+      <c r="F29" s="12">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="12">
+        <v>50</v>
+      </c>
+      <c r="C30" s="12">
+        <v>83</v>
+      </c>
+      <c r="D30" s="12">
+        <v>58</v>
+      </c>
+      <c r="E30" s="12">
+        <v>54</v>
+      </c>
+      <c r="F30" s="12">
         <v>31</v>
       </c>
-      <c r="C5" s="3">
-        <v>9</v>
-      </c>
-      <c r="D5" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="3">
-        <v>32</v>
-      </c>
-      <c r="C6" s="3">
-        <v>10</v>
-      </c>
-      <c r="D6" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="3">
-        <v>33</v>
-      </c>
-      <c r="C7" s="3">
-        <v>11</v>
-      </c>
-      <c r="D7" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="3">
-        <v>34</v>
-      </c>
-      <c r="C8" s="3">
-        <v>13</v>
-      </c>
-      <c r="D8" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="3">
+    </row>
+    <row r="31" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="12">
+        <v>51</v>
+      </c>
+      <c r="C31" s="12">
+        <v>93</v>
+      </c>
+      <c r="D31" s="12">
+        <v>65</v>
+      </c>
+      <c r="E31" s="12">
+        <v>61</v>
+      </c>
+      <c r="F31" s="12">
         <v>35</v>
       </c>
-      <c r="C9" s="3">
-        <v>14</v>
-      </c>
-      <c r="D9" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="3">
-        <v>36</v>
-      </c>
-      <c r="C10" s="3">
-        <v>16</v>
-      </c>
-      <c r="D10" s="3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="3">
-        <v>37</v>
-      </c>
-      <c r="C11" s="3">
-        <v>18</v>
-      </c>
-      <c r="D11" s="3">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="3">
-        <v>38</v>
-      </c>
-      <c r="C12" s="3">
-        <v>20</v>
-      </c>
-      <c r="D12" s="3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="3">
-        <v>39</v>
-      </c>
-      <c r="C13" s="3">
-        <v>23</v>
-      </c>
-      <c r="D13" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="3">
+    </row>
+    <row r="32" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="12">
+        <v>52</v>
+      </c>
+      <c r="C32" s="12">
+        <v>104</v>
+      </c>
+      <c r="D32" s="12">
+        <v>73</v>
+      </c>
+      <c r="E32" s="12">
+        <v>68</v>
+      </c>
+      <c r="F32" s="12">
         <v>40</v>
       </c>
-      <c r="C14" s="3">
-        <v>26</v>
-      </c>
-      <c r="D14" s="3">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="3">
-        <v>41</v>
-      </c>
-      <c r="C15" s="3">
-        <v>29</v>
-      </c>
-      <c r="D15" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="3">
-        <v>42</v>
-      </c>
-      <c r="C16" s="3">
-        <v>33</v>
-      </c>
-      <c r="D16" s="3">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="3">
-        <v>43</v>
-      </c>
-      <c r="C17" s="3">
-        <v>37</v>
-      </c>
-      <c r="D17" s="3">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="3">
-        <v>44</v>
-      </c>
-      <c r="C18" s="3">
-        <v>41</v>
-      </c>
-      <c r="D18" s="3">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="3">
+    </row>
+    <row r="33" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="12">
+        <v>53</v>
+      </c>
+      <c r="C33" s="12">
+        <v>116</v>
+      </c>
+      <c r="D33" s="12">
+        <v>83</v>
+      </c>
+      <c r="E33" s="12">
+        <v>76</v>
+      </c>
+      <c r="F33" s="12">
         <v>45</v>
       </c>
-      <c r="C19" s="3">
-        <v>46</v>
-      </c>
-      <c r="D19" s="3">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="3">
-        <v>46</v>
-      </c>
-      <c r="C20" s="3">
-        <v>52</v>
-      </c>
-      <c r="D20" s="3">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="3">
-        <v>47</v>
-      </c>
-      <c r="C21" s="3">
+    </row>
+    <row r="34" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="12">
+        <v>54</v>
+      </c>
+      <c r="C34" s="12">
+        <v>131</v>
+      </c>
+      <c r="D34" s="12">
+        <v>93</v>
+      </c>
+      <c r="E34" s="12">
+        <v>86</v>
+      </c>
+      <c r="F34" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="12">
+        <v>55</v>
+      </c>
+      <c r="C35" s="12">
+        <v>147</v>
+      </c>
+      <c r="D35" s="12">
+        <v>104</v>
+      </c>
+      <c r="E35" s="12">
+        <v>96</v>
+      </c>
+      <c r="F35" s="12">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="12">
+        <v>56</v>
+      </c>
+      <c r="C36" s="12">
+        <v>165</v>
+      </c>
+      <c r="D36" s="12">
+        <v>116</v>
+      </c>
+      <c r="E36" s="12">
+        <v>108</v>
+      </c>
+      <c r="F36" s="12">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="12">
+        <v>57</v>
+      </c>
+      <c r="C37" s="12">
+        <v>185</v>
+      </c>
+      <c r="D37" s="12">
+        <v>131</v>
+      </c>
+      <c r="E37" s="12">
+        <v>121</v>
+      </c>
+      <c r="F37" s="12">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="12">
         <v>58</v>
       </c>
-      <c r="D21" s="3">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="3">
-        <v>48</v>
-      </c>
-      <c r="C22" s="3">
+      <c r="C38" s="12">
+        <v>208</v>
+      </c>
+      <c r="D38" s="12">
+        <v>147</v>
+      </c>
+      <c r="E38" s="12">
+        <v>136</v>
+      </c>
+      <c r="F38" s="12">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="12">
+        <v>59</v>
+      </c>
+      <c r="C39" s="12">
+        <v>233</v>
+      </c>
+      <c r="D39" s="12">
+        <v>165</v>
+      </c>
+      <c r="E39" s="12">
+        <v>153</v>
+      </c>
+      <c r="F39" s="12">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="12">
+        <v>60</v>
+      </c>
+      <c r="C40" s="12">
+        <v>262</v>
+      </c>
+      <c r="D40" s="12">
+        <v>185</v>
+      </c>
+      <c r="E40" s="12">
+        <v>172</v>
+      </c>
+      <c r="F40" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="12">
+        <v>61</v>
+      </c>
+      <c r="C41" s="12">
+        <v>294</v>
+      </c>
+      <c r="D41" s="12">
+        <v>208</v>
+      </c>
+      <c r="E41" s="12">
+        <v>193</v>
+      </c>
+      <c r="F41" s="12">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="12">
+        <v>62</v>
+      </c>
+      <c r="C42" s="12">
+        <v>330</v>
+      </c>
+      <c r="D42" s="12">
+        <v>233</v>
+      </c>
+      <c r="E42" s="12">
+        <v>216</v>
+      </c>
+      <c r="F42" s="12">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B43" s="12">
+        <v>63</v>
+      </c>
+      <c r="C43" s="12">
+        <v>370</v>
+      </c>
+      <c r="D43" s="12">
+        <v>262</v>
+      </c>
+      <c r="E43" s="12">
+        <v>243</v>
+      </c>
+      <c r="F43" s="12">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="12">
+        <v>64</v>
+      </c>
+      <c r="C44" s="12">
+        <v>415</v>
+      </c>
+      <c r="D44" s="12">
+        <v>294</v>
+      </c>
+      <c r="E44" s="12">
+        <v>273</v>
+      </c>
+      <c r="F44" s="12">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="12">
         <v>65</v>
       </c>
-      <c r="D22" s="3">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="3">
-        <v>49</v>
-      </c>
-      <c r="C23" s="3">
+      <c r="C45" s="12">
+        <v>466</v>
+      </c>
+      <c r="D45" s="12">
+        <v>330</v>
+      </c>
+      <c r="E45" s="12">
+        <v>306</v>
+      </c>
+      <c r="F45" s="12">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B46" s="12">
+        <v>66</v>
+      </c>
+      <c r="C46" s="12">
+        <v>523</v>
+      </c>
+      <c r="D46" s="12">
+        <v>370</v>
+      </c>
+      <c r="E46" s="12">
+        <v>343</v>
+      </c>
+      <c r="F46" s="12">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B47" s="12">
+        <v>67</v>
+      </c>
+      <c r="C47" s="12">
+        <v>586</v>
+      </c>
+      <c r="D47" s="12">
+        <v>415</v>
+      </c>
+      <c r="E47" s="12">
+        <v>385</v>
+      </c>
+      <c r="F47" s="12">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B48" s="12">
+        <v>68</v>
+      </c>
+      <c r="C48" s="12">
+        <v>658</v>
+      </c>
+      <c r="D48" s="12">
+        <v>466</v>
+      </c>
+      <c r="E48" s="12">
+        <v>432</v>
+      </c>
+      <c r="F48" s="12">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="12">
+        <v>69</v>
+      </c>
+      <c r="C49" s="12">
+        <v>738</v>
+      </c>
+      <c r="D49" s="12">
+        <v>523</v>
+      </c>
+      <c r="E49" s="12">
+        <v>485</v>
+      </c>
+      <c r="F49" s="12">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B50" s="12">
+        <v>70</v>
+      </c>
+      <c r="C50" s="12">
+        <v>828</v>
+      </c>
+      <c r="D50" s="12">
+        <v>586</v>
+      </c>
+      <c r="E50" s="12">
+        <v>544</v>
+      </c>
+      <c r="F50" s="12">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B51" s="12">
+        <v>71</v>
+      </c>
+      <c r="C51" s="12">
+        <v>930</v>
+      </c>
+      <c r="D51" s="12">
+        <v>658</v>
+      </c>
+      <c r="E51" s="12">
+        <v>611</v>
+      </c>
+      <c r="F51" s="12">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B52" s="12">
+        <v>72</v>
+      </c>
+      <c r="C52" s="12">
+        <v>1043</v>
+      </c>
+      <c r="D52" s="12">
+        <v>738</v>
+      </c>
+      <c r="E52" s="12">
+        <v>686</v>
+      </c>
+      <c r="F52" s="12">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B53" s="12">
         <v>73</v>
       </c>
-      <c r="D23" s="3">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="3">
-        <v>50</v>
-      </c>
-      <c r="C24" s="3">
+      <c r="C53" s="12">
+        <v>1170</v>
+      </c>
+      <c r="D53" s="12">
+        <v>828</v>
+      </c>
+      <c r="E53" s="12">
+        <v>769</v>
+      </c>
+      <c r="F53" s="12">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="12">
+        <v>74</v>
+      </c>
+      <c r="C54" s="12">
+        <v>1313</v>
+      </c>
+      <c r="D54" s="12">
+        <v>930</v>
+      </c>
+      <c r="E54" s="12">
+        <v>863</v>
+      </c>
+      <c r="F54" s="12">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="12">
+        <v>75</v>
+      </c>
+      <c r="C55" s="12">
+        <v>1474</v>
+      </c>
+      <c r="D55" s="12">
+        <v>1043</v>
+      </c>
+      <c r="E55" s="12">
+        <v>969</v>
+      </c>
+      <c r="F55" s="12">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B56" s="12">
+        <v>76</v>
+      </c>
+      <c r="C56" s="12">
+        <v>1654</v>
+      </c>
+      <c r="D56" s="12">
+        <v>1170</v>
+      </c>
+      <c r="E56" s="12">
+        <v>1087</v>
+      </c>
+      <c r="F56" s="12">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B57" s="12">
+        <v>77</v>
+      </c>
+      <c r="C57" s="12">
+        <v>1855</v>
+      </c>
+      <c r="D57" s="12">
+        <v>1313</v>
+      </c>
+      <c r="E57" s="12">
+        <v>1219</v>
+      </c>
+      <c r="F57" s="12">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B58" s="12">
+        <v>78</v>
+      </c>
+      <c r="C58" s="12">
+        <v>2082</v>
+      </c>
+      <c r="D58" s="12">
+        <v>1474</v>
+      </c>
+      <c r="E58" s="12">
+        <v>1368</v>
+      </c>
+      <c r="F58" s="12">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="12">
+        <v>79</v>
+      </c>
+      <c r="C59" s="12">
+        <v>2336</v>
+      </c>
+      <c r="D59" s="12">
+        <v>1654</v>
+      </c>
+      <c r="E59" s="12">
+        <v>1535</v>
+      </c>
+      <c r="F59" s="12">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B60" s="12">
+        <v>80</v>
+      </c>
+      <c r="C60" s="12">
+        <v>2621</v>
+      </c>
+      <c r="D60" s="12">
+        <v>1855</v>
+      </c>
+      <c r="E60" s="12">
+        <v>1723</v>
+      </c>
+      <c r="F60" s="12">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B61" s="12">
+        <v>81</v>
+      </c>
+      <c r="C61" s="12">
+        <v>2941</v>
+      </c>
+      <c r="D61" s="12">
+        <v>2082</v>
+      </c>
+      <c r="E61" s="12">
+        <v>1933</v>
+      </c>
+      <c r="F61" s="12">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="12">
+        <v>82</v>
+      </c>
+      <c r="C62" s="12">
+        <v>3300</v>
+      </c>
+      <c r="D62" s="12">
+        <v>2336</v>
+      </c>
+      <c r="E62" s="12">
+        <v>2169</v>
+      </c>
+      <c r="F62" s="12">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="12">
         <v>83</v>
       </c>
-      <c r="D24" s="3">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="3">
-        <v>51</v>
-      </c>
-      <c r="C25" s="3">
+      <c r="C63" s="12">
+        <v>3702</v>
+      </c>
+      <c r="D63" s="12">
+        <v>2621</v>
+      </c>
+      <c r="E63" s="12">
+        <v>2434</v>
+      </c>
+      <c r="F63" s="12">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B64" s="12">
+        <v>84</v>
+      </c>
+      <c r="C64" s="12">
+        <v>4154</v>
+      </c>
+      <c r="D64" s="12">
+        <v>2941</v>
+      </c>
+      <c r="E64" s="12">
+        <v>2731</v>
+      </c>
+      <c r="F64" s="12">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="12">
+        <v>85</v>
+      </c>
+      <c r="C65" s="12">
+        <v>4661</v>
+      </c>
+      <c r="D65" s="12">
+        <v>3300</v>
+      </c>
+      <c r="E65" s="12">
+        <v>3064</v>
+      </c>
+      <c r="F65" s="12">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B66" s="12">
+        <v>86</v>
+      </c>
+      <c r="C66" s="12">
+        <v>5230</v>
+      </c>
+      <c r="D66" s="12">
+        <v>3702</v>
+      </c>
+      <c r="E66" s="12">
+        <v>3438</v>
+      </c>
+      <c r="F66" s="12">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B67" s="12">
+        <v>87</v>
+      </c>
+      <c r="C67" s="12">
+        <v>5868</v>
+      </c>
+      <c r="D67" s="12">
+        <v>4154</v>
+      </c>
+      <c r="E67" s="12">
+        <v>3857</v>
+      </c>
+      <c r="F67" s="12">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B68" s="12">
+        <v>88</v>
+      </c>
+      <c r="C68" s="12">
+        <v>6564</v>
+      </c>
+      <c r="D68" s="12">
+        <v>4661</v>
+      </c>
+      <c r="E68" s="12">
+        <v>4328</v>
+      </c>
+      <c r="F68" s="12">
+        <v>2534</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B69" s="12">
+        <v>89</v>
+      </c>
+      <c r="C69" s="12">
+        <v>7388</v>
+      </c>
+      <c r="D69" s="12">
+        <v>5230</v>
+      </c>
+      <c r="E69" s="12">
+        <v>4856</v>
+      </c>
+      <c r="F69" s="12">
+        <v>2843</v>
+      </c>
+    </row>
+    <row r="70" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B70" s="12">
+        <v>90</v>
+      </c>
+      <c r="C70" s="12">
+        <v>8289</v>
+      </c>
+      <c r="D70" s="12">
+        <v>5868</v>
+      </c>
+      <c r="E70" s="12">
+        <v>5449</v>
+      </c>
+      <c r="F70" s="12">
+        <v>3190</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B71" s="12">
+        <v>91</v>
+      </c>
+      <c r="C71" s="12">
+        <v>9301</v>
+      </c>
+      <c r="D71" s="12">
+        <v>6564</v>
+      </c>
+      <c r="E71" s="12">
+        <v>6114</v>
+      </c>
+      <c r="F71" s="12">
+        <v>3580</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B72" s="12">
+        <v>92</v>
+      </c>
+      <c r="C72" s="12">
+        <v>10436</v>
+      </c>
+      <c r="D72" s="12">
+        <v>7388</v>
+      </c>
+      <c r="E72" s="12">
+        <v>6860</v>
+      </c>
+      <c r="F72" s="12">
+        <v>4016</v>
+      </c>
+    </row>
+    <row r="73" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B73" s="12">
         <v>93</v>
       </c>
-      <c r="D25" s="3">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="3">
-        <v>52</v>
-      </c>
-      <c r="C26" s="3">
+      <c r="C73" s="12">
+        <v>11709</v>
+      </c>
+      <c r="D73" s="12">
+        <v>8289</v>
+      </c>
+      <c r="E73" s="12">
+        <v>7697</v>
+      </c>
+      <c r="F73" s="12">
+        <v>4507</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B74" s="12">
+        <v>94</v>
+      </c>
+      <c r="C74" s="12">
+        <v>13138</v>
+      </c>
+      <c r="D74" s="12">
+        <v>9301</v>
+      </c>
+      <c r="E74" s="12">
+        <v>8636</v>
+      </c>
+      <c r="F74" s="12">
+        <v>5056</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B75" s="12">
+        <v>95</v>
+      </c>
+      <c r="C75" s="12">
+        <v>14741</v>
+      </c>
+      <c r="D75" s="12">
+        <v>10436</v>
+      </c>
+      <c r="E75" s="12">
+        <v>9690</v>
+      </c>
+      <c r="F75" s="12">
+        <v>5673</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B76" s="12">
+        <v>96</v>
+      </c>
+      <c r="C76" s="12">
+        <v>16540</v>
+      </c>
+      <c r="D76" s="12">
+        <v>11709</v>
+      </c>
+      <c r="E76" s="12">
+        <v>10872</v>
+      </c>
+      <c r="F76" s="12">
+        <v>6366</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B77" s="12">
+        <v>97</v>
+      </c>
+      <c r="C77" s="12">
+        <v>18558</v>
+      </c>
+      <c r="D77" s="12">
+        <v>13138</v>
+      </c>
+      <c r="E77" s="12">
+        <v>12199</v>
+      </c>
+      <c r="F77" s="12">
+        <v>7143</v>
+      </c>
+    </row>
+    <row r="78" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B78" s="12">
+        <v>98</v>
+      </c>
+      <c r="C78" s="12">
+        <v>20822</v>
+      </c>
+      <c r="D78" s="12">
+        <v>14741</v>
+      </c>
+      <c r="E78" s="12">
+        <v>13687</v>
+      </c>
+      <c r="F78" s="12">
+        <v>8014</v>
+      </c>
+    </row>
+    <row r="79" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B79" s="12">
+        <v>99</v>
+      </c>
+      <c r="C79" s="12">
+        <v>23363</v>
+      </c>
+      <c r="D79" s="12">
+        <v>16540</v>
+      </c>
+      <c r="E79" s="12">
+        <v>15358</v>
+      </c>
+      <c r="F79" s="12">
+        <v>8992</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B80" s="12">
+        <v>100</v>
+      </c>
+      <c r="C80" s="12">
+        <v>26214</v>
+      </c>
+      <c r="D80" s="12">
+        <v>18558</v>
+      </c>
+      <c r="E80" s="12">
+        <v>17232</v>
+      </c>
+      <c r="F80" s="12">
+        <v>10089</v>
+      </c>
+    </row>
+    <row r="81" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B81" s="12">
+        <v>101</v>
+      </c>
+      <c r="C81" s="12">
+        <v>29413</v>
+      </c>
+      <c r="D81" s="12">
+        <v>20822</v>
+      </c>
+      <c r="E81" s="12">
+        <v>19334</v>
+      </c>
+      <c r="F81" s="12">
+        <v>11321</v>
+      </c>
+    </row>
+    <row r="82" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B82" s="12">
+        <v>102</v>
+      </c>
+      <c r="C82" s="12">
+        <v>33001</v>
+      </c>
+      <c r="D82" s="12">
+        <v>23363</v>
+      </c>
+      <c r="E82" s="12">
+        <v>21693</v>
+      </c>
+      <c r="F82" s="12">
+        <v>12702</v>
+      </c>
+    </row>
+    <row r="83" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B83" s="12">
+        <v>103</v>
+      </c>
+      <c r="C83" s="12">
+        <v>37028</v>
+      </c>
+      <c r="D83" s="12">
+        <v>26214</v>
+      </c>
+      <c r="E83" s="12">
+        <v>24340</v>
+      </c>
+      <c r="F83" s="12">
+        <v>14252</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B84" s="12">
         <v>104</v>
       </c>
-      <c r="D26" s="3">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="3">
-        <v>53</v>
-      </c>
-      <c r="C27" s="3">
+      <c r="C84" s="12">
+        <v>41547</v>
+      </c>
+      <c r="D84" s="12">
+        <v>29413</v>
+      </c>
+      <c r="E84" s="12">
+        <v>27311</v>
+      </c>
+      <c r="F84" s="12">
+        <v>15991</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B85" s="12">
+        <v>105</v>
+      </c>
+      <c r="C85" s="12">
+        <v>46616</v>
+      </c>
+      <c r="D85" s="12">
+        <v>33001</v>
+      </c>
+      <c r="E85" s="12">
+        <v>30643</v>
+      </c>
+      <c r="F85" s="12">
+        <v>17942</v>
+      </c>
+    </row>
+    <row r="86" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B86" s="12">
+        <v>106</v>
+      </c>
+      <c r="C86" s="12">
+        <v>52304</v>
+      </c>
+      <c r="D86" s="12">
+        <v>37028</v>
+      </c>
+      <c r="E86" s="12">
+        <v>34382</v>
+      </c>
+      <c r="F86" s="12">
+        <v>20132</v>
+      </c>
+    </row>
+    <row r="87" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B87" s="12">
+        <v>107</v>
+      </c>
+      <c r="C87" s="12">
+        <v>58686</v>
+      </c>
+      <c r="D87" s="12">
+        <v>41547</v>
+      </c>
+      <c r="E87" s="12">
+        <v>38577</v>
+      </c>
+      <c r="F87" s="12">
+        <v>22588</v>
+      </c>
+    </row>
+    <row r="88" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B88" s="12">
+        <v>108</v>
+      </c>
+      <c r="C88" s="12">
+        <v>65847</v>
+      </c>
+      <c r="D88" s="12">
+        <v>46616</v>
+      </c>
+      <c r="E88" s="12">
+        <v>43285</v>
+      </c>
+      <c r="F88" s="12">
+        <v>25344</v>
+      </c>
+    </row>
+    <row r="89" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B89" s="12">
+        <v>109</v>
+      </c>
+      <c r="C89" s="12">
+        <v>73882</v>
+      </c>
+      <c r="D89" s="12">
+        <v>52304</v>
+      </c>
+      <c r="E89" s="12">
+        <v>48566</v>
+      </c>
+      <c r="F89" s="12">
+        <v>28437</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B90" s="12">
+        <v>110</v>
+      </c>
+      <c r="C90" s="12">
+        <v>82897</v>
+      </c>
+      <c r="D90" s="12">
+        <v>58686</v>
+      </c>
+      <c r="E90" s="12">
+        <v>54492</v>
+      </c>
+      <c r="F90" s="12">
+        <v>31907</v>
+      </c>
+    </row>
+    <row r="91" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B91" s="12">
+        <v>111</v>
+      </c>
+      <c r="C91" s="12">
+        <v>93012</v>
+      </c>
+      <c r="D91" s="12">
+        <v>65847</v>
+      </c>
+      <c r="E91" s="12">
+        <v>61141</v>
+      </c>
+      <c r="F91" s="12">
+        <v>35800</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B92" s="12">
+        <v>112</v>
+      </c>
+      <c r="C92" s="12">
+        <v>104361</v>
+      </c>
+      <c r="D92" s="12">
+        <v>73882</v>
+      </c>
+      <c r="E92" s="12">
+        <v>68602</v>
+      </c>
+      <c r="F92" s="12">
+        <v>40168</v>
+      </c>
+    </row>
+    <row r="93" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B93" s="12">
+        <v>113</v>
+      </c>
+      <c r="C93" s="12">
+        <v>117095</v>
+      </c>
+      <c r="D93" s="12">
+        <v>82897</v>
+      </c>
+      <c r="E93" s="12">
+        <v>76972</v>
+      </c>
+      <c r="F93" s="12">
+        <v>45070</v>
+      </c>
+    </row>
+    <row r="94" spans="2:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B94" s="12">
+        <v>114</v>
+      </c>
+      <c r="C94" s="12">
+        <v>131383</v>
+      </c>
+      <c r="D94" s="12">
+        <v>93012</v>
+      </c>
+      <c r="E94" s="12">
+        <v>86365</v>
+      </c>
+      <c r="F94" s="12">
+        <v>50569</v>
+      </c>
+    </row>
+    <row r="95" spans="2:6" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="B95" s="12">
+        <v>115</v>
+      </c>
+      <c r="C95" s="12">
+        <v>147414</v>
+      </c>
+      <c r="D95" s="12">
+        <v>104361</v>
+      </c>
+      <c r="E95" s="12">
+        <v>96903</v>
+      </c>
+      <c r="F95" s="12">
+        <v>56739</v>
+      </c>
+    </row>
+    <row r="96" spans="2:6" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="B96" s="12">
         <v>116</v>
       </c>
-      <c r="D27" s="3">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="3">
-        <v>54</v>
-      </c>
-      <c r="C28" s="3">
-        <v>131</v>
-      </c>
-      <c r="D28" s="3">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="3">
-        <v>55</v>
-      </c>
-      <c r="C29" s="3">
-        <v>147</v>
-      </c>
-      <c r="D29" s="3">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="3">
-        <v>56</v>
-      </c>
-      <c r="C30" s="3">
-        <v>165</v>
-      </c>
-      <c r="D30" s="3">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="3">
-        <v>57</v>
-      </c>
-      <c r="C31" s="3">
-        <v>185</v>
-      </c>
-      <c r="D31" s="3">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="3">
-        <v>58</v>
-      </c>
-      <c r="C32" s="3">
-        <v>208</v>
-      </c>
-      <c r="D32" s="3">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="3">
-        <v>59</v>
-      </c>
-      <c r="C33" s="3">
-        <v>233</v>
-      </c>
-      <c r="D33" s="3">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="3">
-        <v>60</v>
-      </c>
-      <c r="C34" s="3">
-        <v>262</v>
-      </c>
-      <c r="D34" s="3">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="3">
-        <v>61</v>
-      </c>
-      <c r="C35" s="3">
-        <v>294</v>
-      </c>
-      <c r="D35" s="3">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="3">
-        <v>62</v>
-      </c>
-      <c r="C36" s="3">
-        <v>330</v>
-      </c>
-      <c r="D36" s="3">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="3">
-        <v>63</v>
-      </c>
-      <c r="C37" s="3">
-        <v>370</v>
-      </c>
-      <c r="D37" s="3">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="3">
-        <v>64</v>
-      </c>
-      <c r="C38" s="3">
-        <v>415</v>
-      </c>
-      <c r="D38" s="3">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="3">
-        <v>65</v>
-      </c>
-      <c r="C39" s="3">
-        <v>466</v>
-      </c>
-      <c r="D39" s="3">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="3">
-        <v>66</v>
-      </c>
-      <c r="C40" s="3">
-        <v>523</v>
-      </c>
-      <c r="D40" s="3">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="3">
-        <v>67</v>
-      </c>
-      <c r="C41" s="3">
-        <v>586</v>
-      </c>
-      <c r="D41" s="3">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="3">
-        <v>68</v>
-      </c>
-      <c r="C42" s="3">
-        <v>658</v>
-      </c>
-      <c r="D42" s="3">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="3">
-        <v>69</v>
-      </c>
-      <c r="C43" s="3">
-        <v>738</v>
-      </c>
-      <c r="D43" s="3">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="3">
-        <v>70</v>
-      </c>
-      <c r="C44" s="3">
-        <v>828</v>
-      </c>
-      <c r="D44" s="3">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="3">
-        <v>71</v>
-      </c>
-      <c r="C45" s="3">
-        <v>930</v>
-      </c>
-      <c r="D45" s="3">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="46" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="3">
-        <v>72</v>
-      </c>
-      <c r="C46" s="11">
-        <v>1043</v>
-      </c>
-      <c r="D46" s="3">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="3">
-        <v>73</v>
-      </c>
-      <c r="C47" s="11">
-        <v>1170</v>
-      </c>
-      <c r="D47" s="3">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="48" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="3">
-        <v>74</v>
-      </c>
-      <c r="C48" s="11">
-        <v>1313</v>
-      </c>
-      <c r="D48" s="3">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="49" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="3">
-        <v>75</v>
-      </c>
-      <c r="C49" s="11">
-        <v>1474</v>
-      </c>
-      <c r="D49" s="11">
-        <v>1043</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="3">
-        <v>76</v>
-      </c>
-      <c r="C50" s="11">
-        <v>1654</v>
-      </c>
-      <c r="D50" s="11">
-        <v>1170</v>
-      </c>
-    </row>
-    <row r="51" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="3">
-        <v>77</v>
-      </c>
-      <c r="C51" s="11">
-        <v>1855</v>
-      </c>
-      <c r="D51" s="11">
-        <v>1313</v>
-      </c>
-    </row>
-    <row r="52" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="3">
-        <v>78</v>
-      </c>
-      <c r="C52" s="11">
-        <v>2082</v>
-      </c>
-      <c r="D52" s="11">
-        <v>1474</v>
-      </c>
-    </row>
-    <row r="53" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="3">
-        <v>79</v>
-      </c>
-      <c r="C53" s="11">
-        <v>2336</v>
-      </c>
-      <c r="D53" s="11">
-        <v>1654</v>
-      </c>
-    </row>
-    <row r="54" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="3">
-        <v>80</v>
-      </c>
-      <c r="C54" s="11">
-        <v>2621</v>
-      </c>
-      <c r="D54" s="11">
-        <v>1855</v>
-      </c>
-    </row>
-    <row r="55" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="3">
-        <v>81</v>
-      </c>
-      <c r="C55" s="11">
-        <v>2941</v>
-      </c>
-      <c r="D55" s="11">
-        <v>2082</v>
-      </c>
-    </row>
-    <row r="56" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="3">
-        <v>82</v>
-      </c>
-      <c r="C56" s="11">
-        <v>3300</v>
-      </c>
-      <c r="D56" s="11">
-        <v>2336</v>
-      </c>
-    </row>
-    <row r="57" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="3">
-        <v>83</v>
-      </c>
-      <c r="C57" s="11">
-        <v>3702</v>
-      </c>
-      <c r="D57" s="11">
-        <v>2621</v>
-      </c>
-    </row>
-    <row r="58" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="3">
-        <v>84</v>
-      </c>
-      <c r="C58" s="11">
-        <v>4154</v>
-      </c>
-      <c r="D58" s="11">
-        <v>2941</v>
-      </c>
-    </row>
-    <row r="59" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="3">
-        <v>85</v>
-      </c>
-      <c r="C59" s="11">
-        <v>4661</v>
-      </c>
-      <c r="D59" s="11">
-        <v>3300</v>
-      </c>
-    </row>
-    <row r="60" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="3">
-        <v>86</v>
-      </c>
-      <c r="C60" s="11">
-        <v>5230</v>
-      </c>
-      <c r="D60" s="11">
-        <v>3702</v>
-      </c>
-    </row>
-    <row r="61" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="3">
-        <v>87</v>
-      </c>
-      <c r="C61" s="11">
-        <v>5868</v>
-      </c>
-      <c r="D61" s="11">
-        <v>4154</v>
-      </c>
-    </row>
-    <row r="62" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="3">
-        <v>88</v>
-      </c>
-      <c r="C62" s="11">
-        <v>6564</v>
-      </c>
-      <c r="D62" s="11">
-        <v>4661</v>
-      </c>
-    </row>
-    <row r="63" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="3">
-        <v>89</v>
-      </c>
-      <c r="C63" s="11">
-        <v>7388</v>
-      </c>
-      <c r="D63" s="11">
-        <v>5230</v>
-      </c>
-    </row>
-    <row r="64" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="3">
-        <v>90</v>
-      </c>
-      <c r="C64" s="11">
-        <v>8289</v>
-      </c>
-      <c r="D64" s="11">
-        <v>5868</v>
-      </c>
-    </row>
-    <row r="65" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="3">
-        <v>91</v>
-      </c>
-      <c r="C65" s="11">
-        <v>9301</v>
-      </c>
-      <c r="D65" s="11">
-        <v>6564</v>
-      </c>
-    </row>
-    <row r="66" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="3">
-        <v>92</v>
-      </c>
-      <c r="C66" s="11">
-        <v>10436</v>
-      </c>
-      <c r="D66" s="11">
-        <v>7388</v>
-      </c>
-    </row>
-    <row r="67" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="3">
-        <v>93</v>
-      </c>
-      <c r="C67" s="11">
-        <v>11709</v>
-      </c>
-      <c r="D67" s="11">
-        <v>8289</v>
-      </c>
-    </row>
-    <row r="68" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="3">
-        <v>94</v>
-      </c>
-      <c r="C68" s="11">
-        <v>13138</v>
-      </c>
-      <c r="D68" s="11">
-        <v>9301</v>
-      </c>
-    </row>
-    <row r="69" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="3">
-        <v>95</v>
-      </c>
-      <c r="C69" s="11">
-        <v>14741</v>
-      </c>
-      <c r="D69" s="11">
-        <v>10436</v>
-      </c>
-    </row>
-    <row r="70" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="3">
-        <v>96</v>
-      </c>
-      <c r="C70" s="11">
-        <v>16540</v>
-      </c>
-      <c r="D70" s="11">
-        <v>11709</v>
-      </c>
-    </row>
-    <row r="71" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="3">
-        <v>97</v>
-      </c>
-      <c r="C71" s="11">
-        <v>18558</v>
-      </c>
-      <c r="D71" s="11">
-        <v>13138</v>
-      </c>
-    </row>
-    <row r="72" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B72" s="3">
-        <v>98</v>
-      </c>
-      <c r="C72" s="11">
-        <v>20822</v>
-      </c>
-      <c r="D72" s="11">
-        <v>14741</v>
-      </c>
-    </row>
-    <row r="73" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="3">
-        <v>99</v>
-      </c>
-      <c r="C73" s="11">
-        <v>23363</v>
-      </c>
-      <c r="D73" s="11">
-        <v>16540</v>
-      </c>
-    </row>
-    <row r="74" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="3">
-        <v>100</v>
-      </c>
-      <c r="C74" s="11">
-        <v>26214</v>
-      </c>
-      <c r="D74" s="11">
-        <v>18558</v>
-      </c>
-    </row>
-    <row r="75" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="3">
-        <v>101</v>
-      </c>
-      <c r="C75" s="11">
-        <v>29413</v>
-      </c>
-      <c r="D75" s="11">
-        <v>20822</v>
-      </c>
-    </row>
-    <row r="76" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="3">
-        <v>102</v>
-      </c>
-      <c r="C76" s="11">
-        <v>33001</v>
-      </c>
-      <c r="D76" s="11">
-        <v>23363</v>
-      </c>
-    </row>
-    <row r="77" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B77" s="3">
-        <v>103</v>
-      </c>
-      <c r="C77" s="11">
-        <v>37028</v>
-      </c>
-      <c r="D77" s="11">
-        <v>26214</v>
-      </c>
-    </row>
-    <row r="78" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="3">
-        <v>104</v>
-      </c>
-      <c r="C78" s="11">
-        <v>41547</v>
-      </c>
-      <c r="D78" s="11">
-        <v>29413</v>
-      </c>
-    </row>
-    <row r="79" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B79" s="3">
-        <v>105</v>
-      </c>
-      <c r="C79" s="11">
-        <v>46616</v>
-      </c>
-      <c r="D79" s="11">
-        <v>33001</v>
-      </c>
-    </row>
-    <row r="80" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="3">
-        <v>106</v>
-      </c>
-      <c r="C80" s="11">
-        <v>52304</v>
-      </c>
-      <c r="D80" s="11">
-        <v>37028</v>
-      </c>
-    </row>
-    <row r="81" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B81" s="3">
-        <v>107</v>
-      </c>
-      <c r="C81" s="11">
-        <v>58686</v>
-      </c>
-      <c r="D81" s="11">
-        <v>41547</v>
-      </c>
-    </row>
-    <row r="82" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="3">
-        <v>108</v>
-      </c>
-      <c r="C82" s="11">
-        <v>65847</v>
-      </c>
-      <c r="D82" s="11">
-        <v>46616</v>
-      </c>
-    </row>
-    <row r="83" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B83" s="3">
-        <v>109</v>
-      </c>
-      <c r="C83" s="11">
-        <v>73882</v>
-      </c>
-      <c r="D83" s="11">
-        <v>52304</v>
-      </c>
-    </row>
-    <row r="84" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B84" s="3">
-        <v>110</v>
-      </c>
-      <c r="C84" s="11">
-        <v>82897</v>
-      </c>
-      <c r="D84" s="11">
-        <v>58686</v>
-      </c>
-    </row>
-    <row r="85" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B85" s="3">
-        <v>111</v>
-      </c>
-      <c r="C85" s="11">
-        <v>93012</v>
-      </c>
-      <c r="D85" s="11">
-        <v>65847</v>
-      </c>
-    </row>
-    <row r="86" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B86" s="3">
-        <v>112</v>
-      </c>
-      <c r="C86" s="11">
-        <v>104361</v>
-      </c>
-      <c r="D86" s="11">
-        <v>73882</v>
-      </c>
-    </row>
-    <row r="87" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B87" s="3">
-        <v>113</v>
-      </c>
-      <c r="C87" s="11">
+      <c r="C96" s="12">
+        <v>165401</v>
+      </c>
+      <c r="D96" s="12">
         <v>117095</v>
       </c>
-      <c r="D87" s="11">
-        <v>82897</v>
-      </c>
-    </row>
-    <row r="88" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B88" s="3">
-        <v>114</v>
-      </c>
-      <c r="C88" s="11">
+      <c r="E96" s="12">
+        <v>108727</v>
+      </c>
+      <c r="F96" s="12">
+        <v>63663</v>
+      </c>
+    </row>
+    <row r="97" spans="2:6" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="B97" s="12">
+        <v>117</v>
+      </c>
+      <c r="C97" s="12">
+        <v>185583</v>
+      </c>
+      <c r="D97" s="12">
         <v>131383</v>
       </c>
-      <c r="D88" s="11">
-        <v>93012</v>
-      </c>
-    </row>
-    <row r="89" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B89" s="3">
-        <v>115</v>
-      </c>
-      <c r="C89" s="11">
+      <c r="E97" s="12">
+        <v>121993</v>
+      </c>
+      <c r="F97" s="12">
+        <v>71431</v>
+      </c>
+    </row>
+    <row r="98" spans="2:6" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="B98" s="12">
+        <v>118</v>
+      </c>
+      <c r="C98" s="12">
+        <v>208228</v>
+      </c>
+      <c r="D98" s="12">
         <v>147414</v>
       </c>
-      <c r="D89" s="11">
-        <v>104361</v>
-      </c>
-    </row>
-    <row r="90" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B90" s="3">
-        <v>116</v>
-      </c>
-      <c r="C90" s="11">
+      <c r="E98" s="12">
+        <v>136879</v>
+      </c>
+      <c r="F98" s="12">
+        <v>80147</v>
+      </c>
+    </row>
+    <row r="99" spans="2:6" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="B99" s="12">
+        <v>119</v>
+      </c>
+      <c r="C99" s="12">
+        <v>233636</v>
+      </c>
+      <c r="D99" s="12">
         <v>165401</v>
       </c>
-      <c r="D90" s="11">
-        <v>117095</v>
-      </c>
-    </row>
-    <row r="91" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B91" s="3">
-        <v>117</v>
-      </c>
-      <c r="C91" s="11">
+      <c r="E99" s="12">
+        <v>153581</v>
+      </c>
+      <c r="F99" s="12">
+        <v>89926</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="B100" s="12">
+        <v>120</v>
+      </c>
+      <c r="C100" s="12">
+        <v>262143</v>
+      </c>
+      <c r="D100" s="12">
         <v>185583</v>
       </c>
-      <c r="D91" s="11">
-        <v>131383</v>
-      </c>
-    </row>
-    <row r="92" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B92" s="3">
-        <v>118</v>
-      </c>
-      <c r="C92" s="11">
-        <v>208228</v>
-      </c>
-      <c r="D92" s="11">
-        <v>147414</v>
-      </c>
-    </row>
-    <row r="93" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B93" s="3">
-        <v>119</v>
-      </c>
-      <c r="C93" s="11">
-        <v>233636</v>
-      </c>
-      <c r="D93" s="11">
-        <v>165401</v>
-      </c>
-    </row>
-    <row r="94" spans="2:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B94" s="3">
-        <v>120</v>
-      </c>
-      <c r="C94" s="11">
-        <v>262143</v>
-      </c>
-      <c r="D94" s="11">
-        <v>185583</v>
+      <c r="E100" s="12">
+        <v>172321</v>
+      </c>
+      <c r="F100" s="12">
+        <v>100899</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B4:F6"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5609,7 +6667,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:AE18"/>
+  <dimension ref="B2:AI18"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.1" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.625" style="1" customWidth="1"/>
@@ -5620,97 +6678,105 @@
     <col min="16" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:31" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E2" s="17" t="s">
+    <row r="2" spans="2:35" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="P2" s="14" t="s">
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+      <c r="P2" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="14"/>
-      <c r="T2" s="14"/>
-      <c r="U2" s="14"/>
-      <c r="V2" s="14"/>
-      <c r="W2" s="14"/>
-      <c r="X2" s="14"/>
-      <c r="Y2" s="14"/>
-      <c r="Z2" s="14"/>
-      <c r="AA2" s="14"/>
-      <c r="AB2" s="14"/>
-      <c r="AC2" s="14"/>
-    </row>
-    <row r="3" spans="2:31" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q2" s="21"/>
+      <c r="R2" s="21"/>
+      <c r="S2" s="21"/>
+      <c r="T2" s="21"/>
+      <c r="U2" s="21"/>
+      <c r="V2" s="21"/>
+      <c r="W2" s="21"/>
+      <c r="X2" s="21"/>
+      <c r="Y2" s="21"/>
+      <c r="Z2" s="21"/>
+      <c r="AA2" s="21"/>
+      <c r="AB2" s="21"/>
+      <c r="AC2" s="21"/>
+    </row>
+    <row r="3" spans="2:35" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="8" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18" t="s">
+      <c r="F3" s="19"/>
+      <c r="G3" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18" t="s">
+      <c r="H3" s="19"/>
+      <c r="I3" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18" t="s">
+      <c r="J3" s="19"/>
+      <c r="K3" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18">
+      <c r="L3" s="19"/>
+      <c r="M3" s="19">
         <v>5020</v>
       </c>
-      <c r="N3" s="18"/>
-      <c r="P3" s="13" t="s">
+      <c r="N3" s="19"/>
+      <c r="P3" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13" t="s">
+      <c r="Q3" s="20"/>
+      <c r="R3" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13" t="s">
+      <c r="S3" s="20"/>
+      <c r="T3" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="U3" s="13"/>
-      <c r="V3" s="13" t="s">
+      <c r="U3" s="20"/>
+      <c r="V3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="W3" s="13"/>
-      <c r="X3" s="13" t="s">
+      <c r="W3" s="20"/>
+      <c r="X3" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="15" t="s">
+      <c r="Y3" s="20"/>
+      <c r="Z3" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="AA3" s="16"/>
-      <c r="AB3" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC3" s="13"/>
-      <c r="AD3" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE3" s="16"/>
-    </row>
-    <row r="4" spans="2:31" ht="11.25" x14ac:dyDescent="0.3">
+      <c r="AA3" s="17"/>
+      <c r="AB3" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC3" s="20"/>
+      <c r="AD3" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE3" s="17"/>
+      <c r="AF3" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG3" s="17"/>
+      <c r="AH3" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="AI3" s="17"/>
+    </row>
+    <row r="4" spans="2:35" ht="11.25" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>45</v>
       </c>
@@ -5790,13 +6856,25 @@
         <v>12</v>
       </c>
       <c r="AD4" s="5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE4" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="2:31" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="AF4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI4" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="2:35" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>50</v>
       </c>
@@ -5875,14 +6953,26 @@
       <c r="AC5" s="6">
         <v>24</v>
       </c>
-      <c r="AD5" s="6">
+      <c r="AD5" s="10">
         <v>30</v>
       </c>
-      <c r="AE5" s="6">
+      <c r="AE5" s="10">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="2:31" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF5" s="10">
+        <v>54</v>
+      </c>
+      <c r="AG5" s="10">
+        <v>17</v>
+      </c>
+      <c r="AH5" s="10">
+        <v>31</v>
+      </c>
+      <c r="AI5" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="2:35" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>55</v>
       </c>
@@ -5961,14 +7051,26 @@
       <c r="AC6" s="6">
         <v>33</v>
       </c>
-      <c r="AD6" s="6">
+      <c r="AD6" s="10">
         <v>54</v>
       </c>
-      <c r="AE6" s="6">
+      <c r="AE6" s="10">
         <v>31</v>
       </c>
-    </row>
-    <row r="7" spans="2:31" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF6" s="10">
+        <v>96</v>
+      </c>
+      <c r="AG6" s="10">
+        <v>30</v>
+      </c>
+      <c r="AH6" s="10">
+        <v>56</v>
+      </c>
+      <c r="AI6" s="10">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="2:35" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>60</v>
       </c>
@@ -6043,14 +7145,26 @@
       </c>
       <c r="AB7" s="6"/>
       <c r="AC7" s="6"/>
-      <c r="AD7" s="6">
+      <c r="AD7" s="10">
         <v>96</v>
       </c>
-      <c r="AE7" s="6">
+      <c r="AE7" s="10">
         <v>56</v>
       </c>
-    </row>
-    <row r="8" spans="2:31" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF7" s="10">
+        <v>172</v>
+      </c>
+      <c r="AG7" s="10">
+        <v>54</v>
+      </c>
+      <c r="AH7" s="10">
+        <v>100</v>
+      </c>
+      <c r="AI7" s="10">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="2:35" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>65</v>
       </c>
@@ -6129,14 +7243,26 @@
       <c r="AC8" s="6">
         <v>125</v>
       </c>
-      <c r="AD8" s="6">
+      <c r="AD8" s="10">
         <v>172</v>
       </c>
-      <c r="AE8" s="6">
+      <c r="AE8" s="10">
         <v>100</v>
       </c>
-    </row>
-    <row r="9" spans="2:31" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF8" s="10">
+        <v>306</v>
+      </c>
+      <c r="AG8" s="10">
+        <v>96</v>
+      </c>
+      <c r="AH8" s="10">
+        <v>179</v>
+      </c>
+      <c r="AI8" s="10">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="2:35" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
         <v>70</v>
       </c>
@@ -6211,14 +7337,26 @@
       </c>
       <c r="AB9" s="6"/>
       <c r="AC9" s="6"/>
-      <c r="AD9" s="6">
+      <c r="AD9" s="10">
         <v>306</v>
       </c>
-      <c r="AE9" s="6">
+      <c r="AE9" s="10">
         <v>179</v>
       </c>
-    </row>
-    <row r="10" spans="2:31" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF9" s="10">
+        <v>544</v>
+      </c>
+      <c r="AG9" s="10">
+        <v>172</v>
+      </c>
+      <c r="AH9" s="10">
+        <v>319</v>
+      </c>
+      <c r="AI9" s="10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="2:35" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <v>75</v>
       </c>
@@ -6297,14 +7435,26 @@
       <c r="AC10" s="6">
         <v>389</v>
       </c>
-      <c r="AD10" s="6">
+      <c r="AD10" s="10">
         <v>544</v>
       </c>
-      <c r="AE10" s="6">
+      <c r="AE10" s="10">
         <v>319</v>
       </c>
-    </row>
-    <row r="11" spans="2:31" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF10" s="10">
+        <v>969</v>
+      </c>
+      <c r="AG10" s="10">
+        <v>306</v>
+      </c>
+      <c r="AH10" s="10">
+        <v>567</v>
+      </c>
+      <c r="AI10" s="10">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="11" spans="2:35" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <v>80</v>
       </c>
@@ -6379,14 +7529,26 @@
       </c>
       <c r="AB11" s="6"/>
       <c r="AC11" s="6"/>
-      <c r="AD11" s="6">
+      <c r="AD11" s="10">
         <v>969</v>
       </c>
-      <c r="AE11" s="6">
+      <c r="AE11" s="10">
         <v>567</v>
       </c>
-    </row>
-    <row r="12" spans="2:31" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF11" s="10">
+        <v>1723</v>
+      </c>
+      <c r="AG11" s="10">
+        <v>544</v>
+      </c>
+      <c r="AH11" s="10">
+        <v>1008</v>
+      </c>
+      <c r="AI11" s="10">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="12" spans="2:35" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <v>85</v>
       </c>
@@ -6465,14 +7627,26 @@
       <c r="AC12" s="6">
         <v>1118</v>
       </c>
-      <c r="AD12" s="6">
+      <c r="AD12" s="10">
         <v>1723</v>
       </c>
-      <c r="AE12" s="6">
+      <c r="AE12" s="10">
         <v>1008</v>
       </c>
-    </row>
-    <row r="13" spans="2:31" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF12" s="10">
+        <v>3064</v>
+      </c>
+      <c r="AG12" s="10">
+        <v>969</v>
+      </c>
+      <c r="AH12" s="10">
+        <v>1794</v>
+      </c>
+      <c r="AI12" s="10">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="13" spans="2:35" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
         <v>90</v>
       </c>
@@ -6547,14 +7721,26 @@
       </c>
       <c r="AB13" s="6"/>
       <c r="AC13" s="6"/>
-      <c r="AD13" s="6">
+      <c r="AD13" s="10">
         <v>3064</v>
       </c>
-      <c r="AE13" s="6">
+      <c r="AE13" s="10">
         <v>1794</v>
       </c>
-    </row>
-    <row r="14" spans="2:31" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF13" s="10">
+        <v>5449</v>
+      </c>
+      <c r="AG13" s="10">
+        <v>1723</v>
+      </c>
+      <c r="AH13" s="10">
+        <v>3190</v>
+      </c>
+      <c r="AI13" s="10">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="14" spans="2:35" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
         <v>95</v>
       </c>
@@ -6633,14 +7819,26 @@
       <c r="AC14" s="6">
         <v>3364</v>
       </c>
-      <c r="AD14" s="6">
+      <c r="AD14" s="10">
         <v>5449</v>
       </c>
-      <c r="AE14" s="6">
+      <c r="AE14" s="10">
         <v>3190</v>
       </c>
-    </row>
-    <row r="15" spans="2:31" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF14" s="10">
+        <v>9690</v>
+      </c>
+      <c r="AG14" s="10">
+        <v>3064</v>
+      </c>
+      <c r="AH14" s="10">
+        <v>5673</v>
+      </c>
+      <c r="AI14" s="10">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="15" spans="2:35" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
         <v>100</v>
       </c>
@@ -6715,14 +7913,26 @@
       </c>
       <c r="AB15" s="6"/>
       <c r="AC15" s="6"/>
-      <c r="AD15" s="6">
+      <c r="AD15" s="10">
         <v>9690</v>
       </c>
-      <c r="AE15" s="6">
+      <c r="AE15" s="10">
         <v>5673</v>
       </c>
-    </row>
-    <row r="16" spans="2:31" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF15" s="10">
+        <v>17232</v>
+      </c>
+      <c r="AG15" s="10">
+        <v>5449</v>
+      </c>
+      <c r="AH15" s="10">
+        <v>10089</v>
+      </c>
+      <c r="AI15" s="10">
+        <v>3190</v>
+      </c>
+    </row>
+    <row r="16" spans="2:35" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
         <v>105</v>
       </c>
@@ -6801,14 +8011,26 @@
       <c r="AC16" s="6">
         <v>11048</v>
       </c>
-      <c r="AD16" s="6">
+      <c r="AD16" s="10">
         <v>17232</v>
       </c>
-      <c r="AE16" s="6">
+      <c r="AE16" s="10">
         <v>10089</v>
       </c>
-    </row>
-    <row r="17" spans="2:31" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF16" s="10">
+        <v>30643</v>
+      </c>
+      <c r="AG16" s="10">
+        <v>9690</v>
+      </c>
+      <c r="AH16" s="10">
+        <v>17942</v>
+      </c>
+      <c r="AI16" s="10">
+        <v>5673</v>
+      </c>
+    </row>
+    <row r="17" spans="2:35" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="2">
         <v>110</v>
       </c>
@@ -6883,14 +8105,26 @@
       </c>
       <c r="AB17" s="6"/>
       <c r="AC17" s="6"/>
-      <c r="AD17" s="6">
+      <c r="AD17" s="10">
         <v>30643</v>
       </c>
-      <c r="AE17" s="6">
+      <c r="AE17" s="10">
         <v>17942</v>
       </c>
-    </row>
-    <row r="18" spans="2:31" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF17" s="10">
+        <v>54492</v>
+      </c>
+      <c r="AG17" s="10">
+        <v>17232</v>
+      </c>
+      <c r="AH17" s="10">
+        <v>31907</v>
+      </c>
+      <c r="AI17" s="10">
+        <v>10089</v>
+      </c>
+    </row>
+    <row r="18" spans="2:35" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E18" s="2">
         <v>58167</v>
       </c>
@@ -6963,15 +8197,29 @@
       <c r="AC18" s="6">
         <v>36281</v>
       </c>
-      <c r="AD18" s="6">
+      <c r="AD18" s="10">
         <v>54492</v>
       </c>
-      <c r="AE18" s="6">
+      <c r="AE18" s="10">
         <v>31907</v>
       </c>
+      <c r="AF18" s="10">
+        <v>96903</v>
+      </c>
+      <c r="AG18" s="10">
+        <v>30643</v>
+      </c>
+      <c r="AH18" s="10">
+        <v>56739</v>
+      </c>
+      <c r="AI18" s="10">
+        <v>17942</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="17">
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="AH3:AI3"/>
     <mergeCell ref="AD3:AE3"/>
     <mergeCell ref="E2:N2"/>
     <mergeCell ref="M3:N3"/>
